--- a/docs/open-items.xlsx
+++ b/docs/open-items.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Open items'!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Open items'!$A$4:$K$46</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Open items'!$A$4:$K$49</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="224">
   <si>
     <t xml:space="preserve">Read me</t>
   </si>
@@ -311,6 +311,18 @@
     <t xml:space="preserve">3.4</t>
   </si>
   <si>
+    <t xml:space="preserve">Brands whose door is the till</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A coffee chain identifies a shopper at the point of sale and hands the reward over at the same counter. Qumo has no till door and no point of sale integration, and both sit behind items 4.1 and 4.2. Worth costing only if brands of that shape are a target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/seattle-coffee-review.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">USSD, or not</t>
   </si>
   <si>
@@ -320,7 +332,7 @@
     <t xml:space="preserve">docs/competitive-position.md</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5</t>
+    <t xml:space="preserve">3.6</t>
   </si>
   <si>
     <t xml:space="preserve">Language</t>
@@ -335,13 +347,37 @@
     <t xml:space="preserve">4. Product gaps</t>
   </si>
   <si>
+    <t xml:space="preserve">A coupon cannot be redeemed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A brand honouring coupons by eye today has no defence against one code being used at every counter, every time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate from item 4.3 and worse. A completed stamp card issues a real coupon and nothing anywhere can mark it used: REDEEMED is in schema.prisma and in no TypeScript file. CouponFraudEvent.ALREADY_REDEEMED therefore can never fire, so the same screenshot works at every counter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A stamp card cannot be earned from a till slip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the award form's own default of 500 basis points, a R100 basket awards 500 stamps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The slip path resolves campaigns through one filter, PERCENT_OF_SPEND, so the only way to get stamps out of a slip is a share-of-spend rule in stamps, which multiplies stamps by rands. A flat-per-slip rule fixes it and removes the reason anyone would configure the broken combination.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Redemption</t>
   </si>
   <si>
     <t xml:space="preserve">REDEMPTION_AVAILABLE is false. The largest unfinished edge, and CPA section 35 has views about it.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2</t>
+    <t xml:space="preserve">4.4</t>
   </si>
   <si>
     <t xml:space="preserve">Correct-the-read</t>
@@ -350,7 +386,7 @@
     <t xml:space="preserve">Proposed and not built: let a shopper fix a misread slip in the moment, identity fields only, never the amount. It is what makes photo capture defensible without storing anybody's photograph.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3</t>
+    <t xml:space="preserve">4.5</t>
   </si>
   <si>
     <t xml:space="preserve">A reader implementation, once one is chosen</t>
@@ -359,7 +395,7 @@
     <t xml:space="preserve">Plus the capture screen and published accuracy standards. Blocked on item 3.3.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4</t>
+    <t xml:space="preserve">4.6</t>
   </si>
   <si>
     <t xml:space="preserve">Referral</t>
@@ -368,7 +404,7 @@
     <t xml:space="preserve">Once there are shoppers to refer anybody.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5</t>
+    <t xml:space="preserve">4.7</t>
   </si>
   <si>
     <t xml:space="preserve">WhatsApp</t>
@@ -377,7 +413,7 @@
     <t xml:space="preserve">Planned, not built. Needs its own consent copy and version.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6</t>
+    <t xml:space="preserve">4.8</t>
   </si>
   <si>
     <t xml:space="preserve">SMS re-consent has no path</t>
@@ -1400,7 +1436,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -1902,7 +1938,7 @@
       </c>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
         <v>93</v>
       </c>
@@ -1931,7 +1967,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>97</v>
       </c>
@@ -1955,21 +1991,23 @@
       <c r="I21" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>102</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>59</v>
@@ -1985,15 +2023,15 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>47</v>
@@ -2005,24 +2043,26 @@
         <v>34</v>
       </c>
       <c r="G23" s="10"/>
-      <c r="H23" s="8"/>
+      <c r="H23" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="I23" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>47</v>
@@ -2034,24 +2074,26 @@
         <v>34</v>
       </c>
       <c r="G24" s="10"/>
-      <c r="H24" s="8"/>
+      <c r="H24" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="I24" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>47</v>
@@ -2065,20 +2107,20 @@
       <c r="G25" s="10"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>47</v>
@@ -2092,20 +2134,22 @@
       <c r="G26" s="10"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="J26" s="8"/>
+        <v>118</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>47</v>
@@ -2119,25 +2163,25 @@
       <c r="G27" s="10"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="K27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>59</v>
@@ -2148,23 +2192,23 @@
       <c r="G28" s="10"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>59</v>
@@ -2175,23 +2219,23 @@
       <c r="G29" s="10"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>59</v>
@@ -2202,22 +2246,22 @@
       <c r="G30" s="10"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>43</v>
@@ -2231,20 +2275,20 @@
       <c r="G31" s="10"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>43</v>
@@ -2258,20 +2302,20 @@
       <c r="G32" s="10"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>43</v>
@@ -2285,20 +2329,22 @@
       <c r="G33" s="10"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="J33" s="8"/>
+        <v>141</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>142</v>
+      </c>
       <c r="K33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>43</v>
@@ -2307,16 +2353,14 @@
         <v>59</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="8" t="s">
         <v>145</v>
       </c>
+      <c r="J34" s="8"/>
       <c r="K34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2324,7 +2368,7 @@
         <v>146</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>147</v>
@@ -2336,164 +2380,166 @@
         <v>59</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="J35" s="8" t="s">
-        <v>149</v>
-      </c>
+      <c r="J35" s="8"/>
       <c r="K35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>151</v>
-      </c>
       <c r="D36" s="8" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>149</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="J36" s="8"/>
       <c r="K36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>157</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="K37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="B38" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>161</v>
-      </c>
       <c r="D38" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="K38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-    </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="B39" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="8" t="s">
+      <c r="D39" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="E39" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="J39" s="8"/>
+        <v>166</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>161</v>
+      </c>
       <c r="K39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="G40" s="10"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>47</v>
@@ -2507,20 +2553,20 @@
       <c r="G41" s="10"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>160</v>
-      </c>
       <c r="C42" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>47</v>
@@ -2534,20 +2580,20 @@
       <c r="G42" s="10"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>47</v>
@@ -2561,98 +2607,179 @@
       <c r="G43" s="10"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="G44" s="10"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="G46" s="10"/>
       <c r="H46" s="8"/>
       <c r="I46" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
     </row>
+    <row r="47" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G48" s="10"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G49" s="10"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K46"/>
+  <autoFilter ref="A4:K49"/>
   <mergeCells count="1">
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F46">
+  <conditionalFormatting sqref="F5:F49">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Done"</formula>
     </cfRule>
@@ -2667,11 +2794,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pick one of the listed statuses." errorStyle="stop" operator="between" prompt="Not started, In progress, Waiting on someone, Blocked, Done, Parked" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F46" type="list">
+    <dataValidation allowBlank="true" error="Pick one of the listed statuses." errorStyle="stop" operator="between" prompt="Not started, In progress, Waiting on someone, Blocked, Done, Parked" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F49" type="list">
       <formula1>"Not started,In progress,Waiting on someone,Blocked,Done,Parked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D46" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D49" type="list">
       <formula1>"Allan,Lawyer,Claude,Allan + lawyer,Lawyer + Claude,Allan + Claude"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2701,12 +2828,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2717,22 +2844,22 @@
         <v>34</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2740,27 +2867,27 @@
         <v>30</v>
       </c>
       <c r="B5" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A5,'Open items'!$F$5:$F$46,B$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A5,'Open items'!$F$5:$F$49,B$4)</f>
         <v>6</v>
       </c>
       <c r="C5" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A5,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A5,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D5" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A5,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A5,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E5" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A5,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A5,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F5" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A5,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A5,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G5" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A5,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A5,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H5" s="15" t="n">
@@ -2773,27 +2900,27 @@
         <v>57</v>
       </c>
       <c r="B6" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A6,'Open items'!$F$5:$F$46,B$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A6,'Open items'!$F$5:$F$49,B$4)</f>
         <v>6</v>
       </c>
       <c r="C6" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A6,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A6,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D6" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A6,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A6,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E6" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A6,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A6,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F6" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A6,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A6,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G6" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A6,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A6,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H6" s="15" t="n">
@@ -2806,93 +2933,93 @@
         <v>79</v>
       </c>
       <c r="B7" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A7,'Open items'!$F$5:$F$46,B$4)</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A7,'Open items'!$F$5:$F$49,B$4)</f>
+        <v>6</v>
       </c>
       <c r="C7" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A7,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A7,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D7" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A7,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A7,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E7" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A7,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A7,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F7" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A7,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A7,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G7" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A7,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A7,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H7" s="15" t="n">
         <f aca="false">SUM(B7:G7)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B8" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A8,'Open items'!$F$5:$F$46,B$4)</f>
-        <v>6</v>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A8,'Open items'!$F$5:$F$49,B$4)</f>
+        <v>8</v>
       </c>
       <c r="C8" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A8,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A8,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D8" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A8,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A8,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E8" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A8,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A8,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F8" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A8,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A8,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G8" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A8,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A8,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H8" s="15" t="n">
         <f aca="false">SUM(B8:G8)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B9" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A9,'Open items'!$F$5:$F$46,B$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A9,'Open items'!$F$5:$F$49,B$4)</f>
         <v>6</v>
       </c>
       <c r="C9" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A9,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A9,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D9" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A9,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A9,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E9" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A9,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A9,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F9" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A9,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A9,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G9" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A9,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A9,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H9" s="15" t="n">
@@ -2902,30 +3029,30 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B10" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A10,'Open items'!$F$5:$F$46,B$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A10,'Open items'!$F$5:$F$49,B$4)</f>
         <v>0</v>
       </c>
       <c r="C10" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A10,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A10,'Open items'!$F$5:$F$49,C$4)</f>
         <v>2</v>
       </c>
       <c r="D10" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A10,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A10,'Open items'!$F$5:$F$49,D$4)</f>
         <v>1</v>
       </c>
       <c r="E10" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A10,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A10,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F10" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A10,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A10,'Open items'!$F$5:$F$49,F$4)</f>
         <v>1</v>
       </c>
       <c r="G10" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A10,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A10,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H10" s="15" t="n">
@@ -2935,30 +3062,30 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B11" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A11,'Open items'!$F$5:$F$46,B$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A11,'Open items'!$F$5:$F$49,B$4)</f>
         <v>6</v>
       </c>
       <c r="C11" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A11,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A11,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D11" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A11,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A11,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E11" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A11,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A11,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F11" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A11,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A11,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G11" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A11,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A11,'Open items'!$F$5:$F$49,G$4)</f>
         <v>0</v>
       </c>
       <c r="H11" s="15" t="n">
@@ -2968,30 +3095,30 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B12" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A12,'Open items'!$F$5:$F$46,B$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A12,'Open items'!$F$5:$F$49,B$4)</f>
         <v>0</v>
       </c>
       <c r="C12" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A12,'Open items'!$F$5:$F$46,C$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A12,'Open items'!$F$5:$F$49,C$4)</f>
         <v>0</v>
       </c>
       <c r="D12" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A12,'Open items'!$F$5:$F$46,D$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A12,'Open items'!$F$5:$F$49,D$4)</f>
         <v>0</v>
       </c>
       <c r="E12" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A12,'Open items'!$F$5:$F$46,E$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A12,'Open items'!$F$5:$F$49,E$4)</f>
         <v>0</v>
       </c>
       <c r="F12" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A12,'Open items'!$F$5:$F$46,F$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A12,'Open items'!$F$5:$F$49,F$4)</f>
         <v>0</v>
       </c>
       <c r="G12" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$B$5:$B$46,$A12,'Open items'!$F$5:$F$46,G$4)</f>
+        <f aca="false">COUNTIFS('Open items'!$B$5:$B$49,$A12,'Open items'!$F$5:$F$49,G$4)</f>
         <v>3</v>
       </c>
       <c r="H12" s="15" t="n">
@@ -3001,11 +3128,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">SUM(B5:B12)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">SUM(C5:C12)</f>
@@ -3029,12 +3156,12 @@
       </c>
       <c r="H13" s="17" t="n">
         <f aca="false">SUM(H5:H12)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3042,10 +3169,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3053,11 +3180,11 @@
         <v>43</v>
       </c>
       <c r="B18" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A18,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked")</f>
-        <v>14</v>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A18,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked")</f>
+        <v>15</v>
       </c>
       <c r="C18" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A18,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked",'Open items'!$E$5:$E$46,"Yes")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A18,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked",'Open items'!$E$5:$E$49,"Yes")</f>
         <v>1</v>
       </c>
     </row>
@@ -3066,11 +3193,11 @@
         <v>32</v>
       </c>
       <c r="B19" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A19,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A19,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked")</f>
         <v>8</v>
       </c>
       <c r="C19" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A19,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked",'Open items'!$E$5:$E$46,"Yes")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A19,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked",'Open items'!$E$5:$E$49,"Yes")</f>
         <v>3</v>
       </c>
     </row>
@@ -3079,11 +3206,11 @@
         <v>47</v>
       </c>
       <c r="B20" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A20,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked")</f>
-        <v>13</v>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A20,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked")</f>
+        <v>15</v>
       </c>
       <c r="C20" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A20,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked",'Open items'!$E$5:$E$46,"Yes")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A20,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked",'Open items'!$E$5:$E$49,"Yes")</f>
         <v>1</v>
       </c>
     </row>
@@ -3092,11 +3219,11 @@
         <v>51</v>
       </c>
       <c r="B21" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A21,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A21,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked")</f>
         <v>1</v>
       </c>
       <c r="C21" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A21,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked",'Open items'!$E$5:$E$46,"Yes")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A21,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked",'Open items'!$E$5:$E$49,"Yes")</f>
         <v>1</v>
       </c>
     </row>
@@ -3105,39 +3232,39 @@
         <v>73</v>
       </c>
       <c r="B22" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A22,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A22,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked")</f>
         <v>1</v>
       </c>
       <c r="C22" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A22,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked",'Open items'!$E$5:$E$46,"Yes")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A22,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked",'Open items'!$E$5:$E$49,"Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B23" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A23,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A23,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked")</f>
         <v>1</v>
       </c>
       <c r="C23" s="14" t="n">
-        <f aca="false">COUNTIFS('Open items'!$D$5:$D$46,$A23,'Open items'!$F$5:$F$46,"&lt;&gt;Done",'Open items'!$F$5:$F$46,"&lt;&gt;Parked",'Open items'!$E$5:$E$46,"Yes")</f>
+        <f aca="false">COUNTIFS('Open items'!$D$5:$D$49,$A23,'Open items'!$F$5:$F$49,"&lt;&gt;Done",'Open items'!$F$5:$F$49,"&lt;&gt;Parked",'Open items'!$E$5:$E$49,"Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">COUNTIFS('Open items'!$E$5:$E$46,"Yes",'Open items'!$F$5:$F$46,"&lt;&gt;Done")</f>
+        <f aca="false">COUNTIFS('Open items'!$E$5:$E$49,"Yes",'Open items'!$F$5:$F$49,"&lt;&gt;Done")</f>
         <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3166,58 +3293,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
